--- a/01_raw_data/Drill_Tower_EVM_Master_Report.xlsx
+++ b/01_raw_data/Drill_Tower_EVM_Master_Report.xlsx
@@ -638,7 +638,7 @@
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="29" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="43" customWidth="1" min="8" max="8"/>
+    <col width="58" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -966,39 +966,73 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>To-Complete Index (BAC)</t>
+          <t>Critical Ratio (CPI*SPI)</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>TCPI_BAC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="C15" s="10">
-        <f>(C8-C9)/(C8-C11)</f>
+        <f>(C9/C11)*(C9/C10)</f>
         <v/>
       </c>
       <c r="D15" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="10" t="n">
+        <v>0.6402</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>0.6402</v>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>🚨 CRITICAL</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>Compound project health ratio (0.7483 * 0.8556 &lt; 0.90)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>To-Complete Index (BAC)</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>TCPI_BAC</t>
+        </is>
+      </c>
+      <c r="C16" s="10">
+        <f>(C8-C9)/(C8-C11)</f>
+        <v/>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="10" t="n">
         <v>5.07</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F16" s="11" t="n">
         <v>6.07</v>
       </c>
-      <c r="G15" s="13" t="inlineStr">
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>🚨 UNVIABLE</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>Requires impossible 607% efficiency</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17"/>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1986,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="69" customWidth="1" min="1" max="1"/>
@@ -1998,6 +2032,7 @@
     <col width="27" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2068,6 +2103,11 @@
           <t>SPI Index</t>
         </is>
       </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Critical Ratio (CR)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="9" t="n">
@@ -2103,6 +2143,10 @@
         <f>D6/C6</f>
         <v/>
       </c>
+      <c r="J6" s="11">
+        <f>H6*I6</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="9" t="n">
@@ -2138,6 +2182,10 @@
         <f>D7/C7</f>
         <v/>
       </c>
+      <c r="J7" s="11">
+        <f>H7*I7</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="9" t="n">
@@ -2173,6 +2221,10 @@
         <f>D8/C8</f>
         <v/>
       </c>
+      <c r="J8" s="11">
+        <f>H8*I8</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="9" t="n">
@@ -2208,6 +2260,10 @@
         <f>D9/C9</f>
         <v/>
       </c>
+      <c r="J9" s="11">
+        <f>H9*I9</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="9" t="n">
@@ -2243,6 +2299,10 @@
         <f>D10/C10</f>
         <v/>
       </c>
+      <c r="J10" s="11">
+        <f>H10*I10</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="9" t="n">
@@ -2278,6 +2338,10 @@
         <f>D11/C11</f>
         <v/>
       </c>
+      <c r="J11" s="11">
+        <f>H11*I11</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="9" t="n">
@@ -2313,6 +2377,10 @@
         <f>D12/C12</f>
         <v/>
       </c>
+      <c r="J12" s="11">
+        <f>H12*I12</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="9" t="n">
@@ -2346,6 +2414,10 @@
       </c>
       <c r="I13" s="31">
         <f>D13/C13</f>
+        <v/>
+      </c>
+      <c r="J13" s="11">
+        <f>H13*I13</f>
         <v/>
       </c>
     </row>
